--- a/WorkBot/refactor/data/orders/Performance Food/Performance Food_Triphammer_2025-10-03.xlsx
+++ b/WorkBot/refactor/data/orders/Performance Food/Performance Food_Triphammer_2025-10-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1472,93 +1472,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EV436</t>
+          <t>J2280</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Veg Blend - SW Fire Roasted (FRZ)</t>
+          <t>Yogurt BIB</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>41.99</t>
+          <t>37.80</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>41.99</t>
+          <t>226.80</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>J2280</t>
+          <t>E9102</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Yogurt BIB</t>
+          <t>Cucumber (English)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>37.80</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>226.80</t>
+          <t>73.44</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>E9102</t>
+          <t>36452</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cucumber (English)</t>
+          <t>Herb - Basil (Fresh)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>73.44</t>
+          <t>127.77</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>36452</t>
+          <t>NH166</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Herb - Basil (Fresh)</t>
+          <t>Lettuce - Arcadian Blend</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1568,39 +1568,147 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>34.51</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>127.77</t>
+          <t>103.53</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NH166</t>
+          <t>FC208</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lettuce - Arcadian Blend</t>
+          <t>Olive - Kalamata (Pitted)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>34.51</t>
+          <t>72.57</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>103.53</t>
+          <t>72.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CP992</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Fries - Steak</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>46.44</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>46.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>RC608</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PKT Sour Cream</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>16.79</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>16.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BK482</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ravioli - Cheese (large) square</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>92.78</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>92.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AV906</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Swiss (Sliced)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>56.88</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>341.28</t>
         </is>
       </c>
     </row>
